--- a/IB_Condition.xlsx
+++ b/IB_Condition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNI\Year 3\PSY310\6.0Intentional_Binding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6307AF-8511-45DF-A70F-C88F068EB5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3394C2E-A159-4925-9B54-6678A64B3B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -199,7 +199,6 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -209,6 +208,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,151 +491,155 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>0.1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>400</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="3">
         <v>0.4</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="8">
         <v>400</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="A4" s="3">
         <v>0.7</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>400</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="A5" s="3">
         <v>0.1</v>
       </c>
-      <c r="B5" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="8">
+        <v>1000</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="A6" s="3">
         <v>0.4</v>
       </c>
-      <c r="B6" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="8">
+        <v>1000</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="A7" s="3">
         <v>0.7</v>
       </c>
-      <c r="B7" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="8">
+        <v>1000</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="A8" s="3">
         <v>0.1</v>
       </c>
-      <c r="B8" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="8">
+        <v>1000</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
+      <c r="A9" s="3">
         <v>0.4</v>
       </c>
-      <c r="B9" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="8">
+        <v>1000</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="4">
+      <c r="A10" s="3">
         <v>0.7</v>
       </c>
-      <c r="B10" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C10" s="5" t="s">
+      <c r="B10" s="8">
+        <v>1000</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <v>0.1</v>
       </c>
-      <c r="B11" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="8">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="4">
+      <c r="A12" s="3">
         <v>0.4</v>
       </c>
-      <c r="B12" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="8">
+        <v>1000</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="6">
+      <c r="A13" s="5">
         <v>0.7</v>
       </c>
-      <c r="B13" s="10">
-        <v>1000</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="9">
+        <v>1000</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>